--- a/output/pdf_financials_xlsx/AVR.xlsx
+++ b/output/pdf_financials_xlsx/AVR.xlsx
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.280001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.497078</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.375379</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.376006</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.140106</v>
       </c>
     </row>
     <row r="35">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.280001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.497078</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.375379</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.376006</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.140106</v>
       </c>
     </row>
     <row r="37">
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.298992</v>
+        <v>0.018991</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.497078</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.389813</v>
+        <v>0.014434</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.434652</v>
+        <v>0.058646</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.175844</v>
+        <v>0.035738</v>
       </c>
     </row>
     <row r="49">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
